--- a/03_Outputs/Transición_ref_subset/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/Transición_ref_subset/04_Cluster/Summary_Stats.xlsx
@@ -406,7 +406,7 @@
         <v>76</v>
       </c>
       <c r="D2">
-        <v>8.089788775818651E-18</v>
+        <v>8.099418203008489E-18</v>
       </c>
       <c r="E2">
         <v>0.9999999999999999</v>
@@ -433,7 +433,7 @@
         <v>76</v>
       </c>
       <c r="D3">
-        <v>-1.92082107255672E-17</v>
+        <v>-1.919768968474868E-17</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>76</v>
       </c>
       <c r="D4">
-        <v>2.90773036587971E-17</v>
+        <v>2.91472061672863E-17</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -487,7 +487,7 @@
         <v>76</v>
       </c>
       <c r="D5">
-        <v>2.841750957356743E-18</v>
+        <v>2.847278961854613E-18</v>
       </c>
       <c r="E5">
         <v>0.9999999999999999</v>
@@ -514,7 +514,7 @@
         <v>76</v>
       </c>
       <c r="D6">
-        <v>-8.966066650093941E-18</v>
+        <v>-8.87904515993392E-18</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -541,7 +541,7 @@
         <v>76</v>
       </c>
       <c r="D7">
-        <v>-9.013143849688707E-18</v>
+        <v>-8.941669872178946E-18</v>
       </c>
       <c r="E7">
         <v>0.9999999999999999</v>
@@ -568,7 +568,7 @@
         <v>76</v>
       </c>
       <c r="D8">
-        <v>-6.198497946644101E-18</v>
+        <v>-6.22702958276214E-18</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -595,7 +595,7 @@
         <v>76</v>
       </c>
       <c r="D9">
-        <v>1.418878264150109E-17</v>
+        <v>1.414384531461517E-17</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>76</v>
       </c>
       <c r="D10">
-        <v>5.226817414099115E-18</v>
+        <v>5.226995736824853E-18</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -676,7 +676,7 @@
         <v>76</v>
       </c>
       <c r="D12">
-        <v>-1.115586972215348E-18</v>
+        <v>-1.10988064499174E-18</v>
       </c>
       <c r="E12">
         <v>0.9999999999999999</v>
@@ -730,7 +730,7 @@
         <v>76</v>
       </c>
       <c r="D14">
-        <v>5.938860057969941E-18</v>
+        <v>5.943139803387647E-18</v>
       </c>
       <c r="E14">
         <v>0.9999999999999999</v>
@@ -757,7 +757,7 @@
         <v>76</v>
       </c>
       <c r="D15">
-        <v>2.328894798134982E-18</v>
+        <v>2.315342270978913E-18</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -811,7 +811,7 @@
         <v>76</v>
       </c>
       <c r="D17">
-        <v>-2.455289946137897E-17</v>
+        <v>-2.455717920679668E-17</v>
       </c>
       <c r="E17">
         <v>0.9999999999999999</v>
@@ -838,7 +838,7 @@
         <v>76</v>
       </c>
       <c r="D18">
-        <v>3.235759477942439E-17</v>
+        <v>3.23604479430362E-17</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>76</v>
       </c>
       <c r="D19">
-        <v>-2.359851623323055E-17</v>
+        <v>-2.359780294232759E-17</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>76</v>
       </c>
       <c r="D20">
-        <v>-1.637680248630325E-17</v>
+        <v>-1.635932685918095E-17</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -919,7 +919,7 @@
         <v>76</v>
       </c>
       <c r="D21">
-        <v>2.742460863665965E-17</v>
+        <v>2.751020354501377E-17</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -946,7 +946,7 @@
         <v>76</v>
       </c>
       <c r="D22">
-        <v>-1.218800165872356E-17</v>
+        <v>-1.218871494962651E-17</v>
       </c>
       <c r="E22">
         <v>0.9999999999999999</v>
@@ -973,7 +973,7 @@
         <v>76</v>
       </c>
       <c r="D23">
-        <v>-1.494915074404684E-17</v>
+        <v>-1.491749846022839E-17</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>76</v>
       </c>
       <c r="D24">
-        <v>2.522909923737651E-18</v>
+        <v>2.5221966328347E-18</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1027,7 +1027,7 @@
         <v>76</v>
       </c>
       <c r="D25">
-        <v>1.412868788292747E-17</v>
+        <v>1.414313202371222E-17</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>76</v>
       </c>
       <c r="D26">
-        <v>-2.611072679342393E-17</v>
+        <v>-2.611215337522983E-17</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1081,7 +1081,7 @@
         <v>76</v>
       </c>
       <c r="D27">
-        <v>-9.604747324596258E-17</v>
+        <v>-9.590481506537237E-17</v>
       </c>
       <c r="E27">
         <v>0.9999999999999999</v>
@@ -1108,7 +1108,7 @@
         <v>76</v>
       </c>
       <c r="D28">
-        <v>1.614890604281041E-17</v>
+        <v>1.605118518910612E-17</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -1135,7 +1135,7 @@
         <v>76</v>
       </c>
       <c r="D29">
-        <v>2.312489107367109E-17</v>
+        <v>2.31320239827006E-17</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>76</v>
       </c>
       <c r="D30">
-        <v>7.100810938877103E-18</v>
+        <v>7.095817902556446E-18</v>
       </c>
       <c r="E30">
         <v>0.9999999999999999</v>
@@ -1189,7 +1189,7 @@
         <v>76</v>
       </c>
       <c r="D31">
-        <v>-1.415311809635354E-17</v>
+        <v>-1.409890798772926E-17</v>
       </c>
       <c r="E31">
         <v>0.9999999999999999</v>
@@ -1216,7 +1216,7 @@
         <v>76</v>
       </c>
       <c r="D32">
-        <v>2.673093323353982E-17</v>
+        <v>2.67327164607972E-17</v>
       </c>
       <c r="E32">
         <v>0.9999999999999999</v>
@@ -1243,7 +1243,7 @@
         <v>76</v>
       </c>
       <c r="D33">
-        <v>-4.843530547398401E-17</v>
+        <v>-4.840392067425417E-17</v>
       </c>
       <c r="E33">
         <v>1</v>

--- a/03_Outputs/Transición_ref_subset/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/Transición_ref_subset/04_Cluster/Summary_Stats.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2">
-        <v>8.099418203008489E-18</v>
+        <v>2.131090893580274E-18</v>
       </c>
       <c r="E2">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>-5.625106683005035</v>
+        <v>-5.635665892332375</v>
       </c>
       <c r="G2">
-        <v>0.8029395732300501</v>
+        <v>0.8147618439581673</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3">
-        <v>-1.919768968474868E-17</v>
+        <v>-3.4970800268043E-17</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>-1.784813568320174</v>
+        <v>-1.793931718439933</v>
       </c>
       <c r="G3">
-        <v>3.087244584349773</v>
+        <v>3.057337903681726</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4">
-        <v>2.91472061672863E-17</v>
+        <v>-1.621163858819721E-17</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F4">
-        <v>-2.981272949304265</v>
+        <v>-2.94876890421336</v>
       </c>
       <c r="G4">
-        <v>2.164270695121573</v>
+        <v>2.170612310458833</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5">
-        <v>2.847278961854613E-18</v>
+        <v>-2.109406850130564E-17</v>
       </c>
       <c r="E5">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>-2.18471987137211</v>
+        <v>-2.119509927200085</v>
       </c>
       <c r="G5">
-        <v>2.377614734223224</v>
+        <v>2.359304598023271</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6">
-        <v>-8.87904515993392E-18</v>
+        <v>1.387778780781446E-17</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>-3.219421053860091</v>
+        <v>-3.242745820668826</v>
       </c>
       <c r="G6">
-        <v>2.888781792698051</v>
+        <v>2.903532789701909</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7">
-        <v>-8.941669872178946E-18</v>
+        <v>9.529788932604979E-18</v>
       </c>
       <c r="E7">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>-2.846421586618676</v>
+        <v>-2.864119511467736</v>
       </c>
       <c r="G7">
-        <v>3.255662725068805</v>
+        <v>3.25418405154998</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8">
-        <v>-6.22702958276214E-18</v>
+        <v>7.859761723135176E-18</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>-3.961771653853615</v>
+        <v>-3.988183028701878</v>
       </c>
       <c r="G8">
-        <v>1.701771906910032</v>
+        <v>1.703939879240778</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9">
-        <v>1.414384531461517E-17</v>
+        <v>-1.781189283369043E-19</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>-1.617150537565037</v>
+        <v>-1.619204130808618</v>
       </c>
       <c r="G9">
-        <v>3.900674601141393</v>
+        <v>3.926937481028953</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D10">
-        <v>5.226995736824853E-18</v>
+        <v>-3.224093408374914E-18</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>-3.368236723330612</v>
+        <v>-3.388406598441609</v>
       </c>
       <c r="G10">
-        <v>1.425523134019099</v>
+        <v>1.420626339351694</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D11">
-        <v>9.951834677972208E-18</v>
+        <v>-1.926782146531382E-17</v>
       </c>
       <c r="E11">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>-2.462816822736243</v>
+        <v>-2.480517247118829</v>
       </c>
       <c r="G11">
-        <v>1.886279192996689</v>
+        <v>1.897060269287998</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12">
-        <v>-1.10988064499174E-18</v>
+        <v>-2.914673372785707E-17</v>
       </c>
       <c r="E12">
         <v>0.9999999999999999</v>
       </c>
       <c r="F12">
-        <v>-2.551373878529555</v>
+        <v>-2.511346442088735</v>
       </c>
       <c r="G12">
-        <v>2.477840019978367</v>
+        <v>2.381233951366469</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13">
-        <v>8.433951636492502E-18</v>
+        <v>2.780063336825169E-17</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13">
-        <v>-2.780119382327323</v>
+        <v>-2.783529630907873</v>
       </c>
       <c r="G13">
-        <v>2.776882585305896</v>
+        <v>2.745761481531492</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14">
-        <v>5.943139803387647E-18</v>
+        <v>2.632780807939476E-17</v>
       </c>
       <c r="E14">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>-1.869168817911686</v>
+        <v>-1.869213226456668</v>
       </c>
       <c r="G14">
-        <v>4.961862223701851</v>
+        <v>4.990764367245033</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15">
-        <v>2.315342270978913E-18</v>
+        <v>1.535202115144085E-17</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>-1.604151183149981</v>
+        <v>-1.599397872924835</v>
       </c>
       <c r="G15">
-        <v>3.062345844514749</v>
+        <v>3.081294017206862</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D16">
-        <v>-2.688821387764051E-17</v>
+        <v>-1.046395901925458E-17</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>-2.845404324371286</v>
+        <v>-2.821066739818653</v>
       </c>
       <c r="G16">
-        <v>2.522262047590355</v>
+        <v>2.454152587047894</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D17">
-        <v>-2.455717920679668E-17</v>
+        <v>-9.787388702528235E-18</v>
       </c>
       <c r="E17">
         <v>0.9999999999999999</v>
       </c>
       <c r="F17">
-        <v>-2.832481409338764</v>
+        <v>-2.848270216122356</v>
       </c>
       <c r="G17">
-        <v>4.89660197774982</v>
+        <v>4.930444661007157</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18">
-        <v>3.23604479430362E-17</v>
+        <v>1.413114966289447E-17</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>-2.642064618991163</v>
+        <v>-2.631293498601509</v>
       </c>
       <c r="G18">
-        <v>3.197591718968152</v>
+        <v>3.212047170322789</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19">
-        <v>-2.359780294232759E-17</v>
+        <v>1.512180419663386E-17</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>-4.547428349889735</v>
+        <v>-4.57484098837957</v>
       </c>
       <c r="G19">
-        <v>1.795088984738537</v>
+        <v>1.808779386941623</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20">
-        <v>-1.635932685918095E-17</v>
+        <v>2.137391938673615E-17</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F20">
-        <v>-3.027007833028209</v>
+        <v>-3.048381070880632</v>
       </c>
       <c r="G20">
-        <v>2.431891645348832</v>
+        <v>2.436477875829866</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D21">
-        <v>2.751020354501377E-17</v>
+        <v>-9.586036870495214E-18</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F21">
-        <v>-2.331760341028503</v>
+        <v>-2.350018714285732</v>
       </c>
       <c r="G21">
-        <v>2.731494473645943</v>
+        <v>2.740915057683263</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D22">
-        <v>-1.218871494962651E-17</v>
+        <v>3.433259944378449E-17</v>
       </c>
       <c r="E22">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>-2.709953504196166</v>
+        <v>-2.718502334446375</v>
       </c>
       <c r="G22">
-        <v>2.162013597543486</v>
+        <v>2.179359967924941</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D23">
-        <v>-1.491749846022839E-17</v>
+        <v>2.053958093326278E-17</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>-2.086123614201124</v>
+        <v>-2.103041791861567</v>
       </c>
       <c r="G23">
-        <v>2.664737300229416</v>
+        <v>2.670829715507786</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24">
-        <v>2.5221966328347E-18</v>
+        <v>-2.486906333823244E-17</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>-2.942921018580972</v>
+        <v>-2.959080182582511</v>
       </c>
       <c r="G24">
-        <v>2.644179372804255</v>
+        <v>2.663663097550589</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25">
-        <v>1.414313202371222E-17</v>
+        <v>-1.973881578569876E-17</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>-2.172643073579311</v>
+        <v>-2.188013937959664</v>
       </c>
       <c r="G25">
-        <v>2.145148456281462</v>
+        <v>2.13880893717449</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26">
-        <v>-2.611215337522983E-17</v>
+        <v>8.628559627261261E-18</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>-1.715754322106879</v>
+        <v>-1.686012016267791</v>
       </c>
       <c r="G26">
-        <v>2.200522705830615</v>
+        <v>2.194951566392466</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D27">
-        <v>-9.590481506537237E-17</v>
+        <v>-4.787667827123652E-17</v>
       </c>
       <c r="E27">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>-3.390406092281797</v>
+        <v>-3.410612719733346</v>
       </c>
       <c r="G27">
-        <v>0.827179383919894</v>
+        <v>0.8203397316648737</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D28">
-        <v>1.605118518910612E-17</v>
+        <v>1.05716752091184E-17</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28">
-        <v>-4.248156234428492</v>
+        <v>-4.120956087221179</v>
       </c>
       <c r="G28">
-        <v>3.006838581276931</v>
+        <v>2.859597636476872</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D29">
-        <v>2.31320239827006E-17</v>
+        <v>-3.021263118833957E-17</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>-1.752587422755153</v>
+        <v>-1.764441227620434</v>
       </c>
       <c r="G29">
-        <v>3.549573545171647</v>
+        <v>3.572941230914172</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D30">
-        <v>7.095817902556446E-18</v>
+        <v>-4.31427981363063E-18</v>
       </c>
       <c r="E30">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>-3.082335241762712</v>
+        <v>-3.104907835731526</v>
       </c>
       <c r="G30">
-        <v>1.918259817639826</v>
+        <v>1.925607938646369</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D31">
-        <v>-1.409890798772926E-17</v>
+        <v>-5.846243402804954E-18</v>
       </c>
       <c r="E31">
         <v>0.9999999999999999</v>
       </c>
       <c r="F31">
-        <v>-3.528711486057531</v>
+        <v>-3.553845018937283</v>
       </c>
       <c r="G31">
-        <v>1.748053832272676</v>
+        <v>1.756556876400256</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D32">
-        <v>2.67327164607972E-17</v>
+        <v>-2.682625946778419E-17</v>
       </c>
       <c r="E32">
         <v>0.9999999999999999</v>
       </c>
       <c r="F32">
-        <v>-1.534037028976285</v>
+        <v>-1.548409410931404</v>
       </c>
       <c r="G32">
-        <v>3.780183516212712</v>
+        <v>3.784545794483664</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D33">
-        <v>-4.840392067425417E-17</v>
+        <v>3.385667693170643E-18</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>-2.070523550143612</v>
+        <v>-1.987874563920327</v>
       </c>
       <c r="G33">
-        <v>1.861462852876034</v>
+        <v>1.833189083124078</v>
       </c>
     </row>
   </sheetData>
